--- a/outputs/quality_summary.xlsx
+++ b/outputs/quality_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120000</v>
+        <v>21055</v>
       </c>
     </row>
     <row r="4">
@@ -461,17 +461,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Missing Reviews</t>
+          <t>Missing Records</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Missing Ratings</t>
+          <t>Total Duplicates</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total Duplicates</t>
+          <t>Invalid Ratings</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -491,31 +491,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Invalid Ratings</t>
+          <t>Total Unique Countries</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total Unique Countries</t>
+          <t>Total Unique Products</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Total Unique Products</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
